--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec66d29316e63c22/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{977C4A75-32B6-4F2F-8798-25CED85A8D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{977C4A75-32B6-4F2F-8798-25CED85A8D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77EC16A-1B70-4069-98DB-10AF212CF5E8}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{B044D872-9C69-4966-96BD-21BAC6DBCF5C}"/>
   </bookViews>
@@ -25,20 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
   <si>
     <t>加工品</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>料理</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一般材料</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>地區</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -51,18 +43,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>所需資源(最大值)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊商店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>杜加德</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>特蕾西</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -71,26 +51,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>原木*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>高級生皮</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>原木*100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>特蕾西的原木音樂盒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蒸蛤罵*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>艾爾文</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -99,10 +67,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>炒蔬菜*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>杜巴頓</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -115,18 +79,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>牛奶燉豬肉*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>格麗娜的蘋果奶茶</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>鮮奶油*4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>瓦爾特</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -135,18 +91,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>特蕾西的原木音樂盒*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>愛心幣</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>真愛魚*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>傑羅姆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -155,18 +103,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>瑞可塔起司沙拉*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>高級絲綢</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>奶油醬牛排*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>潔米</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -175,18 +115,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蘋果舒芙蕾*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>高級布料+</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蘋果鮮奶油蛋糕*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>卡利克斯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -195,10 +127,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>格麗娜的蘋果奶茶*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>芙蘿拉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -207,14 +135,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>格麗娜的手工蛋糕*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(愛心幣商店)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>奈麗絲</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -223,14 +143,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>合金鋼錠*8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>銅礦石*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>阿蘭雯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -239,10 +151,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>馬鈴薯沙拉*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>蕾拉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -251,22 +159,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>無主的小說書*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊文</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(魔物討伐證明)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(格里斯貝恩)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>提爾克納</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -279,10 +171,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>鋼錠*8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>愛麗沙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -291,18 +179,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>雞蛋*3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>煉金術碎屑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>雞蛋*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>迪恩</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -311,10 +191,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>寵物飼料*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>麥爾坎</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -323,18 +199,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>羊毛*50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>麥爾坎枕頭</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蜘蛛網*5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>蘿拉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -343,10 +211,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>麥爾坎枕頭*3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>凱琳</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -355,10 +219,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>牛奶*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>梅文</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -367,18 +227,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>凱琳麵包*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>安黛莉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>凱琳麵包*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>雷納德</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -387,26 +239,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>美乃滋炒肉*2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>麗莎</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>高級煉金催化劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蘋果汁*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>煉金術碎屑*3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>班克爾</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -419,22 +255,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>鱸魚辣魚湯*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>艾琳</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>特殊鋼錠*3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合金鋼錠*30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>康格</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -443,10 +267,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>豆乳防風草蛋糕*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>珍妮佛</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -455,7 +275,243 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>黃豆*10</t>
+    <t>原木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒸蛤蠣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炒蔬菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛奶燉豬肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鮮奶油</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真愛魚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞可塔起司沙拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶油醬牛排</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋果舒芙蕾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋果鮮奶油蛋糕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銅礦石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬鈴薯沙拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鋼錠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雞蛋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寵物飼料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊毛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜘蛛網</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛奶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美乃滋炒肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋果汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱸魚辣魚湯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆乳防風草蛋糕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃豆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>品項類型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所需物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般取得材料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杜加德走廊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>推薦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>★</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊比</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>落葉蛾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用心準備的花束</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉爾摩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最高級絲綢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最高級木材</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>礦山的魔力石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命的魔力石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>礦野的魔力石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝水的瓶子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>傷痕花</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古樸的包裝紙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>休馬斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>尚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卓越繃帶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙威瑪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萊爾特丘陵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜峽谷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡琳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬鈴薯湯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>檸檬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡椒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不死粉末</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>料理成品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>煤炭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分解的裝備零件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐵礦石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有煉金術再燃燒催化劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高級煉金術再燃燒催化劑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +519,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -542,8 +598,36 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0066"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,8 +658,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -639,13 +729,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -670,89 +797,167 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,6 +965,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF0066"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1068,624 +1278,1198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D330BC-B3D7-4A64-AF80-F838651FC966}">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J56"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" style="53" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="53"/>
+    <col min="4" max="4" width="15.875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="53" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.875" style="53" customWidth="1"/>
+    <col min="8" max="8" width="8" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5" style="53" customWidth="1"/>
+    <col min="10" max="10" width="8" style="57" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="53"/>
+    <col min="12" max="12" width="31.75" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" spans="1:10" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="1"/>
+      <c r="D6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
+      <c r="F6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="H6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="4"/>
+      <c r="D7" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H7" s="49">
+        <v>10</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C8" s="1"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H8" s="35">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C9" s="4"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="9" t="s">
+      <c r="H9" s="37">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C10" s="4"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="F10" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="H10" s="35">
+        <v>8</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C11" s="4"/>
+      <c r="D11" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="38">
+        <v>1</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C12" s="4"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="38">
+        <v>1</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C13" s="4"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="36">
+        <v>12</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C14" s="4"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="36">
+        <v>2</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C15" s="4"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="36">
+        <v>8</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C16" s="4"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="36">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C17" s="4"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="36">
+        <v>8</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C18" s="4"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="36">
+        <v>4</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C19" s="4"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="36">
+        <v>10</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C20" s="4"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="36">
+        <v>3</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C21" s="4"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="36">
+        <v>2</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C22" s="4"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="39">
+        <v>1</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C23" s="4"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="36">
+        <v>2</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
-      <c r="C24" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C24" s="4"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="36">
+        <v>10</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J24" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C25" s="4"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="36">
+        <v>1</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C26" s="4"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="36">
+        <v>10</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C27" s="4"/>
+      <c r="D27" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="36">
+        <v>4</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C28" s="4"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="H28" s="36">
+        <v>30</v>
+      </c>
+      <c r="I28" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="4"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C29" s="4"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="36">
+        <v>10</v>
+      </c>
+      <c r="I29" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C30" s="4"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="36">
+        <v>1</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J30" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C31" s="4"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="33">
+        <v>1</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C32" s="4"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="36">
+        <v>40</v>
+      </c>
+      <c r="I32" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C33" s="4"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="36">
+        <v>1</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C34" s="4"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="40">
+        <v>1</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E35" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C35" s="4"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" s="36">
+        <v>3</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C36" s="4"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="41">
+        <v>3</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
-      <c r="C37" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C37" s="4"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="36">
+        <v>1</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C38" s="4"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" s="36">
+        <v>10</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="G39" s="4"/>
-    </row>
-    <row r="40" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C39" s="4"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="36">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="1:7" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="C40" s="4"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" s="36">
+        <v>1</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="13" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" s="61"/>
+      <c r="H41" s="36">
+        <v>1</v>
+      </c>
+      <c r="I41" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="J41" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="36">
+        <v>1</v>
+      </c>
+      <c r="I42" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="J42" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="H43" s="36">
+        <v>10</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J43" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="45"/>
+      <c r="H44" s="36">
+        <v>1</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="45"/>
+      <c r="H45" s="36">
+        <v>1</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46" s="36">
+        <v>10</v>
+      </c>
+      <c r="I46" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="J46" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47" s="36">
+        <v>6</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J47" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" s="36">
+        <v>15</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J48" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="4:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D49" s="17"/>
+      <c r="E49" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="10">
+        <v>5</v>
+      </c>
+      <c r="I49" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="J49" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D50" s="17"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J50" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D51" s="17"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H51" s="10">
+        <v>1</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J51" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="4:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="17"/>
+      <c r="E52" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="H52" s="10">
+        <v>10</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="J52" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D53" s="17"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" s="10">
+        <v>1</v>
+      </c>
+      <c r="I53" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D54" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="25" t="s">
+      <c r="F54" s="14"/>
+      <c r="G54" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="H54" s="10">
+        <v>3</v>
+      </c>
+      <c r="I54" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="J54" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D55" s="21"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="G41" s="4"/>
+      <c r="H55" s="10">
+        <v>15</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="J55" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:10" ht="17" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F56" s="55"/>
+      <c r="G56" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="56">
+        <v>10</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J56" s="56">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="C24:C36"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C8:C23"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D22:D23"/>
+  <mergeCells count="23">
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="D27:D42"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="D43:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="D11:D26"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
